--- a/public/funktionarer-mall.xlsx
+++ b/public/funktionarer-mall.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -133,6 +133,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -506,6 +508,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -534,6 +537,11 @@
           <t>Kompetenser</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -558,7 +566,39 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>simning, cykling, sjukvård</t>
+          <t>simning, cykel, sjukvård</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Funktionär</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Erik Lind</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>erik.lind@example.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0709876543</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>körkort, engelska</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Domare</t>
         </is>
       </c>
     </row>
@@ -573,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -675,7 +715,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Kommaseparerad lista med kompetenser. Giltiga värden:</t>
+          <t>Kommaseparerad lista. Endast dessa värden läses in:</t>
         </is>
       </c>
     </row>
@@ -683,35 +723,39 @@
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  simning, cykling, löpning, sjukvård, teknik, kommunikation, mat, tidstagning, logistik, säkerhet</t>
+          <t xml:space="preserve">  sjukvård, körkort, triathlon, simning, cykel, engelska</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Funktionär, Domare, Sektionsledare eller Tävlingsledare. Lämnas tom används rollen som valts i appen före importen.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>• Rad 2 i fliken Funktionärer är ett EXEMPELRADER – ta bort den eller skriv över den.</t>
-        </is>
-      </c>
+      <c r="B14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>• Kolumnrubriker måste stå på rad 1, i valfri ordning.</t>
+          <t>• Rad 2–3 i fliken Funktionärer är exempelrader – ta bort dem eller skriv över dem.</t>
         </is>
       </c>
     </row>
@@ -719,7 +763,7 @@
       <c r="A16" s="4" t="inlineStr"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>• Filen får vara max 5 MB och ha ändelsen .xlsx eller .xls.</t>
+          <t>• Kolumnrubriker måste stå på rad 1, i valfri ordning.</t>
         </is>
       </c>
     </row>
@@ -727,7 +771,7 @@
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>• Funktionärer som redan finns i systemet hoppas över.</t>
+          <t>• Filen får vara max 5 MB och ha ändelsen .xlsx eller .xls.</t>
         </is>
       </c>
     </row>
@@ -735,7 +779,22 @@
       <c r="A18" s="4" t="inlineStr"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>• Funktionärer som redan finns i systemet hoppas över.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>• Varje ny funktionär får ett inbjudningsmail automatiskt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>• Ett okänt värde i Roll gör att raden hoppas över — den gissas inte.</t>
         </is>
       </c>
     </row>

--- a/public/funktionarer-mall.xlsx
+++ b/public/funktionarer-mall.xlsx
@@ -603,6 +603,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Ogiltig roll" error="Välj en av: Funktionär, Domare, Sektionsledare, Tävlingsledare — eller lämna tomt." promptTitle="Roll" prompt="Välj roll. Lämnas fältet tomt används den roll du väljer i appen före importen." type="list" errorStyle="warning">
+      <formula1>"Funktionär,Domare,Sektionsledare,Tävlingsledare"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -613,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -735,35 +740,34 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Funktionär, Domare, Sektionsledare eller Tävlingsledare. Lämnas tom används rollen som valts i appen före importen.</t>
+          <t>En av värdena nedan. Lämnas tom används rollen som valts i appen.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Funktionär, Domare, Sektionsledare, Tävlingsledare</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>• Rad 2–3 i fliken Funktionärer är exempelrader – ta bort dem eller skriv över dem.</t>
-        </is>
-      </c>
+      <c r="B15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>• Kolumnrubriker måste stå på rad 1, i valfri ordning.</t>
+          <t>• Rad 2–3 i fliken Funktionärer är exempelrader – ta bort dem eller skriv över dem.</t>
         </is>
       </c>
     </row>
@@ -771,7 +775,7 @@
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>• Filen får vara max 5 MB och ha ändelsen .xlsx eller .xls.</t>
+          <t>• Kolumnrubriker måste stå på rad 1, i valfri ordning.</t>
         </is>
       </c>
     </row>
@@ -779,7 +783,7 @@
       <c r="A18" s="4" t="inlineStr"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>• Funktionärer som redan finns i systemet hoppas över.</t>
+          <t>• Filen får vara max 5 MB och ha ändelsen .xlsx eller .xls.</t>
         </is>
       </c>
     </row>
@@ -787,12 +791,20 @@
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
+          <t>• Funktionärer som redan finns i systemet hoppas över.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>• Varje ny funktionär får ett inbjudningsmail automatiskt.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="10" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>• Ett okänt värde i Roll gör att raden hoppas över — den gissas inte.</t>
         </is>
